--- a/datasets/byoai_glossary.xlsx
+++ b/datasets/byoai_glossary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gcuomo/Documents/Books/Open Source AI Book/chapters/Chapter 12 - Commit to Contribute/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gcuomo/Documents/Books/Build Your Own AI/chapters/Chapter 14 - Contributing Open Innovation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC3665C-B789-A94E-B82A-3B2198D39BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A68420-A3F5-3944-8080-0B2870C9ABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="500" windowWidth="38300" windowHeight="18920" xr2:uid="{B0C56F1A-439A-D146-B83A-D517AE3A1B6B}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="38300" windowHeight="18920" xr2:uid="{B0C56F1A-439A-D146-B83A-D517AE3A1B6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Open_Source_AI_Glossary" sheetId="1" r:id="rId1"/>
@@ -2219,7 +2219,7 @@
         <v>2015</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E65">
         <v>210</v>
@@ -2240,7 +2240,7 @@
         <v>1999</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E66">
         <v>210</v>
@@ -2261,7 +2261,7 @@
         <v>2020</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E67">
         <v>210</v>
@@ -2282,7 +2282,7 @@
         <v>2022</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E68">
         <v>320</v>
@@ -2303,7 +2303,7 @@
         <v>2022</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E69">
         <v>320</v>
@@ -2324,7 +2324,7 @@
         <v>2021</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E70">
         <v>300</v>
@@ -2345,7 +2345,7 @@
         <v>2020</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E71">
         <v>300</v>
@@ -2366,7 +2366,7 @@
         <v>2018</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E72">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         <v>2021</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E73">
         <v>600</v>
@@ -2408,7 +2408,7 @@
         <v>2022</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E74">
         <v>600</v>
@@ -2600,7 +2600,7 @@
         <v>2020</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E85">
         <v>320</v>
@@ -2621,7 +2621,7 @@
         <v>2017</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E86">
         <v>220</v>
@@ -2642,7 +2642,7 @@
         <v>2016</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E87">
         <v>110</v>
@@ -2663,7 +2663,7 @@
         <v>2021</v>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E88">
         <v>410</v>
@@ -2684,7 +2684,7 @@
         <v>2025</v>
       </c>
       <c r="D89">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>220</v>
@@ -2705,7 +2705,7 @@
         <v>2008</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E90">
         <v>110</v>
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E91">
         <v>520</v>
@@ -2747,7 +2747,7 @@
         <v>2021</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E92">
         <v>510</v>
@@ -2768,7 +2768,7 @@
         <v>2023</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E94">
         <v>600</v>
@@ -2789,7 +2789,7 @@
         <v>2024</v>
       </c>
       <c r="D95">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E95">
         <v>510</v>
@@ -2810,7 +2810,7 @@
         <v>2024</v>
       </c>
       <c r="D96">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E96">
         <v>600</v>
@@ -2831,7 +2831,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E97">
         <v>320</v>
@@ -2852,7 +2852,7 @@
         <v>2019</v>
       </c>
       <c r="D98">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E98">
         <v>300</v>
@@ -2873,7 +2873,7 @@
         <v>2020</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E99">
         <v>220</v>
@@ -2894,7 +2894,7 @@
         <v>2020</v>
       </c>
       <c r="D100">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E100">
         <v>210</v>
@@ -2915,7 +2915,7 @@
         <v>2002</v>
       </c>
       <c r="D101">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E101">
         <v>520</v>
@@ -2936,7 +2936,7 @@
         <v>2023</v>
       </c>
       <c r="D102">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E102">
         <v>520</v>
@@ -2957,7 +2957,7 @@
         <v>2024</v>
       </c>
       <c r="D103">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E103">
         <v>520</v>
@@ -2978,7 +2978,7 @@
         <v>2023</v>
       </c>
       <c r="D104">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E104">
         <v>210</v>
@@ -2999,7 +2999,7 @@
         <v>2020</v>
       </c>
       <c r="D105">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E105">
         <v>620</v>
@@ -3020,7 +3020,7 @@
         <v>2020</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E107">
         <v>620</v>
@@ -3041,7 +3041,7 @@
         <v>2022</v>
       </c>
       <c r="D108">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E108">
         <v>620</v>
@@ -3062,7 +3062,7 @@
         <v>2018</v>
       </c>
       <c r="D109">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E109">
         <v>420</v>
@@ -3083,7 +3083,7 @@
         <v>2017</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E110">
         <v>420</v>
@@ -3104,7 +3104,7 @@
         <v>2019</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E111">
         <v>620</v>
@@ -3125,7 +3125,7 @@
         <v>2018</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E112">
         <v>620</v>
@@ -3146,7 +3146,7 @@
         <v>2021</v>
       </c>
       <c r="D113">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E113">
         <v>210</v>
@@ -3167,7 +3167,7 @@
         <v>2012</v>
       </c>
       <c r="D114">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E114">
         <v>220</v>
@@ -3188,7 +3188,7 @@
         <v>2022</v>
       </c>
       <c r="D116">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E116">
         <v>400</v>
@@ -3209,7 +3209,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E117">
         <v>400</v>
@@ -3230,7 +3230,7 @@
         <v>2024</v>
       </c>
       <c r="D118">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E118">
         <v>320</v>
@@ -3251,7 +3251,7 @@
         <v>2023</v>
       </c>
       <c r="D119">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E119">
         <v>220</v>
@@ -3272,7 +3272,7 @@
         <v>2020</v>
       </c>
       <c r="D120">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E120">
         <v>220</v>
@@ -3293,7 +3293,7 @@
         <v>2008</v>
       </c>
       <c r="D121">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E121">
         <v>200</v>
@@ -3314,7 +3314,7 @@
         <v>2023</v>
       </c>
       <c r="D122">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E122">
         <v>400</v>
@@ -3335,7 +3335,7 @@
         <v>2020</v>
       </c>
       <c r="D123">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E123">
         <v>620</v>
@@ -3356,7 +3356,7 @@
         <v>2022</v>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E125">
         <v>400</v>
@@ -3377,7 +3377,7 @@
         <v>2024</v>
       </c>
       <c r="D126">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E126">
         <v>400</v>
@@ -3398,7 +3398,7 @@
         <v>1988</v>
       </c>
       <c r="D127">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E127">
         <v>610</v>
@@ -3419,7 +3419,7 @@
         <v>1989</v>
       </c>
       <c r="D128">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E128">
         <v>610</v>
@@ -3440,7 +3440,7 @@
         <v>2004</v>
       </c>
       <c r="D129">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E129">
         <v>610</v>
